--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/118.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/118.xlsx
@@ -426,13 +426,13 @@
         <v>-22.71525270273149</v>
       </c>
       <c r="E2">
-        <v>-22.60416680776892</v>
+        <v>-27.2961783909788</v>
       </c>
       <c r="F2">
-        <v>-1.409877324975252</v>
+        <v>-3.218354128153883</v>
       </c>
       <c r="G2">
-        <v>-19.89352992720042</v>
+        <v>-18.55460695290338</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.617892706761</v>
       </c>
       <c r="E3">
-        <v>-23.15701738006215</v>
+        <v>-27.1125275394062</v>
       </c>
       <c r="F3">
-        <v>-2.336552886036795</v>
+        <v>-3.184386094434686</v>
       </c>
       <c r="G3">
-        <v>-20.4120603534198</v>
+        <v>-18.44342578374623</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.1924304634893</v>
       </c>
       <c r="E4">
-        <v>-23.63507692281786</v>
+        <v>-27.55974533486374</v>
       </c>
       <c r="F4">
-        <v>-1.566150492248185</v>
+        <v>-3.065843405624466</v>
       </c>
       <c r="G4">
-        <v>-19.244164646542</v>
+        <v>-17.95875932561819</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.474765885177</v>
       </c>
       <c r="E5">
-        <v>-25.55776457353399</v>
+        <v>-27.54696590361724</v>
       </c>
       <c r="F5">
-        <v>-0.9378918029429556</v>
+        <v>-3.300287947964782</v>
       </c>
       <c r="G5">
-        <v>-17.69878398997972</v>
+        <v>-17.81160731748468</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.49473877600845</v>
       </c>
       <c r="E6">
-        <v>-23.26105117053778</v>
+        <v>-28.38465616820118</v>
       </c>
       <c r="F6">
-        <v>-1.116230192724258</v>
+        <v>-2.899381319297099</v>
       </c>
       <c r="G6">
-        <v>-17.15085005280293</v>
+        <v>-17.94467174780454</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.32130227627641</v>
       </c>
       <c r="E7">
-        <v>-26.46278254690473</v>
+        <v>-29.16927254526514</v>
       </c>
       <c r="F7">
-        <v>-1.335800569979906</v>
+        <v>-3.188117889584298</v>
       </c>
       <c r="G7">
-        <v>-17.86736890583397</v>
+        <v>-17.31483875280453</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.01685562907941</v>
       </c>
       <c r="E8">
-        <v>-24.66638574615399</v>
+        <v>-29.08697666286367</v>
       </c>
       <c r="F8">
-        <v>-1.607714655051053</v>
+        <v>-2.965088250054559</v>
       </c>
       <c r="G8">
-        <v>-17.42805238662586</v>
+        <v>-17.01915495802111</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.64047823159231</v>
       </c>
       <c r="E9">
-        <v>-24.7593927605622</v>
+        <v>-30.2096789780083</v>
       </c>
       <c r="F9">
-        <v>-2.071017229967205</v>
+        <v>-2.863207343184248</v>
       </c>
       <c r="G9">
-        <v>-17.44070927640358</v>
+        <v>-16.73994104549072</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.27251354469692</v>
       </c>
       <c r="E10">
-        <v>-25.27711547147002</v>
+        <v>-30.05451500291271</v>
       </c>
       <c r="F10">
-        <v>-1.445797820662847</v>
+        <v>-3.114754358922762</v>
       </c>
       <c r="G10">
-        <v>-16.48579289177962</v>
+        <v>-15.9971829039467</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.96781135147173</v>
       </c>
       <c r="E11">
-        <v>-26.79237309122047</v>
+        <v>-31.33806080963965</v>
       </c>
       <c r="F11">
-        <v>-1.113026895977633</v>
+        <v>-2.974114141275462</v>
       </c>
       <c r="G11">
-        <v>-15.83702025014338</v>
+        <v>-15.90741375655356</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.8091107595391</v>
       </c>
       <c r="E12">
-        <v>-27.48862159092605</v>
+        <v>-30.94555326696408</v>
       </c>
       <c r="F12">
-        <v>-0.7185566820297025</v>
+        <v>-2.959472747430981</v>
       </c>
       <c r="G12">
-        <v>-15.04635233460783</v>
+        <v>-15.11775489380249</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.82681057527671</v>
       </c>
       <c r="E13">
-        <v>-28.70989830025983</v>
+        <v>-31.79668955321215</v>
       </c>
       <c r="F13">
-        <v>-1.177675173194314</v>
+        <v>-3.001949771111734</v>
       </c>
       <c r="G13">
-        <v>-14.93991488837274</v>
+        <v>-14.92285236709751</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.05934357433038</v>
       </c>
       <c r="E14">
-        <v>-29.19853399565422</v>
+        <v>-32.13195546080327</v>
       </c>
       <c r="F14">
-        <v>-0.8601230144333324</v>
+        <v>-2.379233688098636</v>
       </c>
       <c r="G14">
-        <v>-12.48762944021707</v>
+        <v>-14.49037208260123</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.4989363394731</v>
       </c>
       <c r="E15">
-        <v>-28.74737895586075</v>
+        <v>-33.77366175254944</v>
       </c>
       <c r="F15">
-        <v>-1.064087778187641</v>
+        <v>-2.435063994312518</v>
       </c>
       <c r="G15">
-        <v>-12.74712570422307</v>
+        <v>-14.3005422326368</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.12135818070282</v>
       </c>
       <c r="E16">
-        <v>-31.12745976978024</v>
+        <v>-33.42062010048806</v>
       </c>
       <c r="F16">
-        <v>-0.3526618300087441</v>
+        <v>-2.396481954159728</v>
       </c>
       <c r="G16">
-        <v>-13.05647674694097</v>
+        <v>-13.65139625452402</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.896967255686233</v>
       </c>
       <c r="E17">
-        <v>-32.03394175014298</v>
+        <v>-34.07856768535607</v>
       </c>
       <c r="F17">
-        <v>-0.7644134447138775</v>
+        <v>-2.329488568825721</v>
       </c>
       <c r="G17">
-        <v>-12.76591001155613</v>
+        <v>-13.82859532215666</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.767207643544198</v>
       </c>
       <c r="E18">
-        <v>-33.01745126434165</v>
+        <v>-34.82765749274745</v>
       </c>
       <c r="F18">
-        <v>0.04191938517116123</v>
+        <v>-2.022465788121723</v>
       </c>
       <c r="G18">
-        <v>-12.05371585694027</v>
+        <v>-13.27052516910487</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.695147398406712</v>
       </c>
       <c r="E19">
-        <v>-32.83630272259227</v>
+        <v>-35.32091778895203</v>
       </c>
       <c r="F19">
-        <v>-0.6671548279511876</v>
+        <v>-2.165451113886348</v>
       </c>
       <c r="G19">
-        <v>-12.30673355824342</v>
+        <v>-12.91350193015324</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.62276825662766</v>
       </c>
       <c r="E20">
-        <v>-32.51007212623831</v>
+        <v>-35.82668548106134</v>
       </c>
       <c r="F20">
-        <v>-0.1006393313810225</v>
+        <v>-2.086555745708918</v>
       </c>
       <c r="G20">
-        <v>-11.55073763625016</v>
+        <v>-12.68248366814711</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.528142370920468</v>
       </c>
       <c r="E21">
-        <v>-34.90451474491906</v>
+        <v>-36.02393186990576</v>
       </c>
       <c r="F21">
-        <v>-0.3661211435694304</v>
+        <v>-2.067403891356193</v>
       </c>
       <c r="G21">
-        <v>-11.61336939899096</v>
+        <v>-12.81261231617426</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.384033553130109</v>
       </c>
       <c r="E22">
-        <v>-35.09327819963251</v>
+        <v>-37.00142338089476</v>
       </c>
       <c r="F22">
-        <v>-0.4233315098763755</v>
+        <v>-1.728276903589298</v>
       </c>
       <c r="G22">
-        <v>-11.00811786968858</v>
+        <v>-12.30825170622315</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.186078026560946</v>
       </c>
       <c r="E23">
-        <v>-34.80730883386145</v>
+        <v>-36.73476644778414</v>
       </c>
       <c r="F23">
-        <v>0.2595596663782865</v>
+        <v>-1.622457109718676</v>
       </c>
       <c r="G23">
-        <v>-11.87096765167922</v>
+        <v>-13.00016037536607</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.946229139050203</v>
       </c>
       <c r="E24">
-        <v>-35.04319462426641</v>
+        <v>-37.44765686526831</v>
       </c>
       <c r="F24">
-        <v>0.1077323469561792</v>
+        <v>-1.380008053165108</v>
       </c>
       <c r="G24">
-        <v>-11.39074729158985</v>
+        <v>-12.11416373183061</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.677267716324067</v>
       </c>
       <c r="E25">
-        <v>-37.00347714389488</v>
+        <v>-37.6692036935743</v>
       </c>
       <c r="F25">
-        <v>-1.152531737417141</v>
+        <v>-1.71211545556068</v>
       </c>
       <c r="G25">
-        <v>-10.85286211034425</v>
+        <v>-12.45598460502819</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.417361987044805</v>
       </c>
       <c r="E26">
-        <v>-34.86989357531529</v>
+        <v>-37.89344180281878</v>
       </c>
       <c r="F26">
-        <v>-0.7330423428024575</v>
+        <v>-1.823812516154165</v>
       </c>
       <c r="G26">
-        <v>-12.28866459492833</v>
+        <v>-12.16225234182662</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.188109492625216</v>
       </c>
       <c r="E27">
-        <v>-35.68057343004821</v>
+        <v>-37.60515702173412</v>
       </c>
       <c r="F27">
-        <v>-0.4893971237192473</v>
+        <v>-1.691189238231159</v>
       </c>
       <c r="G27">
-        <v>-10.58533389060369</v>
+        <v>-12.10322210124925</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.029491100046771</v>
       </c>
       <c r="E28">
-        <v>-36.09247023979374</v>
+        <v>-37.15854351852435</v>
       </c>
       <c r="F28">
-        <v>-0.3185653993421136</v>
+        <v>-1.716409712176793</v>
       </c>
       <c r="G28">
-        <v>-10.99738640404681</v>
+        <v>-12.19141435890936</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.96272587332286</v>
       </c>
       <c r="E29">
-        <v>-33.03690905939848</v>
+        <v>-37.22585461446584</v>
       </c>
       <c r="F29">
-        <v>-0.06805052938748714</v>
+        <v>-1.599723394716246</v>
       </c>
       <c r="G29">
-        <v>-11.16753254516655</v>
+        <v>-12.44449080196581</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.013281143645788</v>
       </c>
       <c r="E30">
-        <v>-34.33440965617683</v>
+        <v>-37.29465463666729</v>
       </c>
       <c r="F30">
-        <v>-0.3193225271482724</v>
+        <v>-1.702825315138284</v>
       </c>
       <c r="G30">
-        <v>-11.80607759486711</v>
+        <v>-12.16812651715663</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.195202496688013</v>
       </c>
       <c r="E31">
-        <v>-34.62154399772452</v>
+        <v>-36.95705670091728</v>
       </c>
       <c r="F31">
-        <v>-1.435200516478833</v>
+        <v>-1.522782145242019</v>
       </c>
       <c r="G31">
-        <v>-11.17694036330063</v>
+        <v>-12.3623515556402</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.498592646849122</v>
       </c>
       <c r="E32">
-        <v>-34.42591528469111</v>
+        <v>-37.12604671651322</v>
       </c>
       <c r="F32">
-        <v>-0.861735845766583</v>
+        <v>-1.664596987866489</v>
       </c>
       <c r="G32">
-        <v>-11.2416685539481</v>
+        <v>-12.26821332717384</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.919553093553983</v>
       </c>
       <c r="E33">
-        <v>-33.58195990082367</v>
+        <v>-37.01112320594389</v>
       </c>
       <c r="F33">
-        <v>-0.615540911817556</v>
+        <v>-1.558990084418386</v>
       </c>
       <c r="G33">
-        <v>-12.67858060498339</v>
+        <v>-12.55467597206145</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.42075069075028</v>
       </c>
       <c r="E34">
-        <v>-33.10901711442015</v>
+        <v>-36.412369265483</v>
       </c>
       <c r="F34">
-        <v>-0.9061446222306645</v>
+        <v>-1.665719425697282</v>
       </c>
       <c r="G34">
-        <v>-11.30795274837187</v>
+        <v>-12.17845070664218</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.979871149774018</v>
       </c>
       <c r="E35">
-        <v>-34.80321792070649</v>
+        <v>-36.27602972071719</v>
       </c>
       <c r="F35">
-        <v>-0.07489450086941665</v>
+        <v>-1.673950084211498</v>
       </c>
       <c r="G35">
-        <v>-10.67036714730855</v>
+        <v>-12.62771807885932</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.55206692562674</v>
       </c>
       <c r="E36">
-        <v>-33.5452725085858</v>
+        <v>-35.46294515662719</v>
       </c>
       <c r="F36">
-        <v>-0.07357739669896544</v>
+        <v>-1.798842209164177</v>
       </c>
       <c r="G36">
-        <v>-11.89269818428336</v>
+        <v>-12.8392184143023</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.10917842952711</v>
       </c>
       <c r="E37">
-        <v>-33.2572826055052</v>
+        <v>-35.55217690194114</v>
       </c>
       <c r="F37">
-        <v>-0.006909559754258428</v>
+        <v>-1.571658307109399</v>
       </c>
       <c r="G37">
-        <v>-12.16414252091059</v>
+        <v>-12.41705709780239</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.62131140430516</v>
       </c>
       <c r="E38">
-        <v>-31.14822790301005</v>
+        <v>-35.17745756336981</v>
       </c>
       <c r="F38">
-        <v>-0.3331040756286477</v>
+        <v>-1.763202530026131</v>
       </c>
       <c r="G38">
-        <v>-11.32009923758203</v>
+        <v>-12.93159308479736</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.06213475759609</v>
       </c>
       <c r="E39">
-        <v>-31.85717276973563</v>
+        <v>-34.06093107346518</v>
       </c>
       <c r="F39">
-        <v>0.3256816092045487</v>
+        <v>-1.47261290185887</v>
       </c>
       <c r="G39">
-        <v>-12.35079640007994</v>
+        <v>-12.8349002427486</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.42786594787983</v>
       </c>
       <c r="E40">
-        <v>-30.62688359182697</v>
+        <v>-34.07420058364801</v>
       </c>
       <c r="F40">
-        <v>0.1411959049270708</v>
+        <v>-1.591248367818204</v>
       </c>
       <c r="G40">
-        <v>-14.30063099795289</v>
+        <v>-13.17837110652775</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.70533388163186</v>
       </c>
       <c r="E41">
-        <v>-30.40362356384949</v>
+        <v>-33.7223758225048</v>
       </c>
       <c r="F41">
-        <v>0.0764962689314154</v>
+        <v>-1.230771866978957</v>
       </c>
       <c r="G41">
-        <v>-12.91290537501417</v>
+        <v>-12.85028927674091</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.90941634928985</v>
       </c>
       <c r="E42">
-        <v>-29.76877198715884</v>
+        <v>-32.91784895034962</v>
       </c>
       <c r="F42">
-        <v>-0.2591076722713735</v>
+        <v>-1.4040621858076</v>
       </c>
       <c r="G42">
-        <v>-13.47999826137285</v>
+        <v>-13.45560738003037</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.03887937980959</v>
       </c>
       <c r="E43">
-        <v>-30.20723481314364</v>
+        <v>-32.37583825961419</v>
       </c>
       <c r="F43">
-        <v>0.3620030347150986</v>
+        <v>-1.36283765363988</v>
       </c>
       <c r="G43">
-        <v>-13.08897399023885</v>
+        <v>-12.89905537495832</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.1138396924893</v>
       </c>
       <c r="E44">
-        <v>-28.33976618359678</v>
+        <v>-32.56578953276655</v>
       </c>
       <c r="F44">
-        <v>-0.09247742736123896</v>
+        <v>-1.421327019216747</v>
       </c>
       <c r="G44">
-        <v>-12.97237160993826</v>
+        <v>-13.16614368423527</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.14323563676885</v>
       </c>
       <c r="E45">
-        <v>-29.04788248466305</v>
+        <v>-32.08710285510079</v>
       </c>
       <c r="F45">
-        <v>0.7294825535776125</v>
+        <v>-1.356571882605104</v>
       </c>
       <c r="G45">
-        <v>-13.14352680384246</v>
+        <v>-13.36392977834113</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.1405348111283</v>
       </c>
       <c r="E46">
-        <v>-28.36987696570178</v>
+        <v>-31.36090762513753</v>
       </c>
       <c r="F46">
-        <v>0.2635043519504178</v>
+        <v>-1.241027883793018</v>
       </c>
       <c r="G46">
-        <v>-13.97916740570452</v>
+        <v>-13.30706515040209</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.12297914808588</v>
       </c>
       <c r="E47">
-        <v>-28.75871306956621</v>
+        <v>-31.11376870864794</v>
       </c>
       <c r="F47">
-        <v>0.5422574382990766</v>
+        <v>-0.9184450497948344</v>
       </c>
       <c r="G47">
-        <v>-13.01264234525618</v>
+        <v>-13.96027736321552</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.09134871073528</v>
       </c>
       <c r="E48">
-        <v>-27.4509934963231</v>
+        <v>-30.72651082508695</v>
       </c>
       <c r="F48">
-        <v>0.3049160951511707</v>
+        <v>-1.018768625947883</v>
       </c>
       <c r="G48">
-        <v>-15.02365582650499</v>
+        <v>-13.73124587784322</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.06783479146013</v>
       </c>
       <c r="E49">
-        <v>-28.70835330564699</v>
+        <v>-30.5089510796528</v>
       </c>
       <c r="F49">
-        <v>1.21018250068736</v>
+        <v>-1.088122030012465</v>
       </c>
       <c r="G49">
-        <v>-13.91995310763348</v>
+        <v>-13.95659490796976</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.04813835294048</v>
       </c>
       <c r="E50">
-        <v>-27.26684010618021</v>
+        <v>-30.07188996249013</v>
       </c>
       <c r="F50">
-        <v>0.8021867037865195</v>
+        <v>-1.239227841426735</v>
       </c>
       <c r="G50">
-        <v>-13.38668241745268</v>
+        <v>-13.98269713239171</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.04983209234104</v>
       </c>
       <c r="E51">
-        <v>-25.25380764951509</v>
+        <v>-29.98752370424322</v>
       </c>
       <c r="F51">
-        <v>0.7522112983756253</v>
+        <v>-1.089348842136012</v>
       </c>
       <c r="G51">
-        <v>-13.22853134235681</v>
+        <v>-13.72830095794445</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.06417949842696</v>
       </c>
       <c r="E52">
-        <v>-25.80596463551707</v>
+        <v>-29.35354637853646</v>
       </c>
       <c r="F52">
-        <v>0.08513199910560024</v>
+        <v>-1.095318057640585</v>
       </c>
       <c r="G52">
-        <v>-13.97656449334718</v>
+        <v>-14.07331346640466</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.09736299344721</v>
       </c>
       <c r="E53">
-        <v>-25.01362328538893</v>
+        <v>-28.23112232855059</v>
       </c>
       <c r="F53">
-        <v>0.3767007575429702</v>
+        <v>-0.8633983791440016</v>
       </c>
       <c r="G53">
-        <v>-15.86055611263226</v>
+        <v>-14.31201514974244</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.14763386647657</v>
       </c>
       <c r="E54">
-        <v>-24.57423429327869</v>
+        <v>-28.93351758101691</v>
       </c>
       <c r="F54">
-        <v>0.4901705243784465</v>
+        <v>-1.266397463871155</v>
       </c>
       <c r="G54">
-        <v>-16.64903883494505</v>
+        <v>-14.08553044571877</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.20441537307398</v>
       </c>
       <c r="E55">
-        <v>-25.00214796249843</v>
+        <v>-28.17145106484111</v>
       </c>
       <c r="F55">
-        <v>0.2763498452656297</v>
+        <v>-1.273344152911032</v>
       </c>
       <c r="G55">
-        <v>-15.46938694517346</v>
+        <v>-14.72785454821497</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.27526597212693</v>
       </c>
       <c r="E56">
-        <v>-24.60259242020462</v>
+        <v>-28.64979094936125</v>
       </c>
       <c r="F56">
-        <v>-0.03260883005871029</v>
+        <v>-1.321247811447525</v>
       </c>
       <c r="G56">
-        <v>-14.54456722419586</v>
+        <v>-14.62521834610453</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.34314608027783</v>
       </c>
       <c r="E57">
-        <v>-24.00800207409687</v>
+        <v>-26.86877971996334</v>
       </c>
       <c r="F57">
-        <v>-0.1754715574477214</v>
+        <v>-1.196418642417459</v>
       </c>
       <c r="G57">
-        <v>-14.59099148451504</v>
+        <v>-15.12795637829226</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.41757098198265</v>
       </c>
       <c r="E58">
-        <v>-23.48626320783793</v>
+        <v>-27.24005604634639</v>
       </c>
       <c r="F58">
-        <v>0.1772406557250857</v>
+        <v>-1.208383581183495</v>
       </c>
       <c r="G58">
-        <v>-16.13375225888013</v>
+        <v>-14.60425798315478</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.48256927298158</v>
       </c>
       <c r="E59">
-        <v>-21.92419059003402</v>
+        <v>-27.23930431509659</v>
       </c>
       <c r="F59">
-        <v>1.084017175036579</v>
+        <v>-1.131907874189642</v>
       </c>
       <c r="G59">
-        <v>-16.55443328319688</v>
+        <v>-15.03835170780837</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.5454208111864</v>
       </c>
       <c r="E60">
-        <v>-22.85811906743689</v>
+        <v>-26.8036033746428</v>
       </c>
       <c r="F60">
-        <v>0.7196233247494928</v>
+        <v>-1.155498949453969</v>
       </c>
       <c r="G60">
-        <v>-16.40646019588946</v>
+        <v>-14.88541690040554</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.59943069740232</v>
       </c>
       <c r="E61">
-        <v>-22.63953555541116</v>
+        <v>-26.95667413123068</v>
       </c>
       <c r="F61">
-        <v>-0.1441468441108581</v>
+        <v>-1.416880342998519</v>
       </c>
       <c r="G61">
-        <v>-15.54877446670004</v>
+        <v>-14.62809408127164</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.64050486075269</v>
       </c>
       <c r="E62">
-        <v>-21.96590959779192</v>
+        <v>-26.20923730194659</v>
       </c>
       <c r="F62">
-        <v>0.1586156430405416</v>
+        <v>-1.279174202691935</v>
       </c>
       <c r="G62">
-        <v>-15.32952283056605</v>
+        <v>-14.90845802679441</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.67389436384869</v>
       </c>
       <c r="E63">
-        <v>-22.82764695594662</v>
+        <v>-26.20282889687238</v>
       </c>
       <c r="F63">
-        <v>0.4309894720202414</v>
+        <v>-1.448790712089162</v>
       </c>
       <c r="G63">
-        <v>-15.18555070934451</v>
+        <v>-15.22559169913842</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.68732955954622</v>
       </c>
       <c r="E64">
-        <v>-20.80049358077708</v>
+        <v>-26.20327744369546</v>
       </c>
       <c r="F64">
-        <v>0.3820992279070146</v>
+        <v>-1.601725558728812</v>
       </c>
       <c r="G64">
-        <v>-15.92042962371256</v>
+        <v>-14.79753401597949</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.69342459470122</v>
       </c>
       <c r="E65">
-        <v>-20.74922218697208</v>
+        <v>-25.94724442515376</v>
       </c>
       <c r="F65">
-        <v>0.5174080729498971</v>
+        <v>-1.527684423531787</v>
       </c>
       <c r="G65">
-        <v>-15.75843161646169</v>
+        <v>-15.17177119939262</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.67975108880317</v>
       </c>
       <c r="E66">
-        <v>-22.23750054595643</v>
+        <v>-25.66717677267527</v>
       </c>
       <c r="F66">
-        <v>-0.3641082107806277</v>
+        <v>-1.597619341513135</v>
       </c>
       <c r="G66">
-        <v>-15.02743096318374</v>
+        <v>-15.40826810892321</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.65956404866224</v>
       </c>
       <c r="E67">
-        <v>-22.37653760147772</v>
+        <v>-25.6615117924282</v>
       </c>
       <c r="F67">
-        <v>0.1083519657734732</v>
+        <v>-1.597507511913757</v>
       </c>
       <c r="G67">
-        <v>-17.10007629199496</v>
+        <v>-15.41378983373341</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.62568753356328</v>
       </c>
       <c r="E68">
-        <v>-19.40773492905246</v>
+        <v>-25.74082151588713</v>
       </c>
       <c r="F68">
-        <v>-0.3671996779278754</v>
+        <v>-1.650677102029846</v>
       </c>
       <c r="G68">
-        <v>-15.58418007947242</v>
+        <v>-15.03875898396458</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.5830388142405</v>
       </c>
       <c r="E69">
-        <v>-19.80969518070334</v>
+        <v>-25.5143427491329</v>
       </c>
       <c r="F69">
-        <v>0.08889775731872679</v>
+        <v>-1.681992703325279</v>
       </c>
       <c r="G69">
-        <v>-15.40690791099124</v>
+        <v>-15.04946042604355</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.53450945630945</v>
       </c>
       <c r="E70">
-        <v>-20.4875906395645</v>
+        <v>-25.73714592386466</v>
       </c>
       <c r="F70">
-        <v>-0.4593265586302224</v>
+        <v>-1.590909565550459</v>
       </c>
       <c r="G70">
-        <v>-14.59065469846278</v>
+        <v>-15.25775998861782</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.47156261189368</v>
       </c>
       <c r="E71">
-        <v>-21.17339796599946</v>
+        <v>-25.81577867387763</v>
       </c>
       <c r="F71">
-        <v>0.5226988555515775</v>
+        <v>-1.59981037329354</v>
       </c>
       <c r="G71">
-        <v>-14.82830294635805</v>
+        <v>-14.76587090557846</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.40641096314839</v>
       </c>
       <c r="E72">
-        <v>-20.57454642507244</v>
+        <v>-25.77113995855838</v>
       </c>
       <c r="F72">
-        <v>0.03003396967579392</v>
+        <v>-1.814611011043868</v>
       </c>
       <c r="G72">
-        <v>-15.50255906594815</v>
+        <v>-15.00824199043906</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.32685001163765</v>
       </c>
       <c r="E73">
-        <v>-20.56604480149051</v>
+        <v>-26.26158853069606</v>
       </c>
       <c r="F73">
-        <v>-0.2782852060135849</v>
+        <v>-1.877619120803007</v>
       </c>
       <c r="G73">
-        <v>-14.81479364847134</v>
+        <v>-14.50959368965331</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.2469838516282</v>
       </c>
       <c r="E74">
-        <v>-20.59887178380196</v>
+        <v>-26.34212345149581</v>
       </c>
       <c r="F74">
-        <v>-0.1272299250108866</v>
+        <v>-2.156705210847591</v>
       </c>
       <c r="G74">
-        <v>-14.48825085262095</v>
+        <v>-15.08482818301936</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.15573306794953</v>
       </c>
       <c r="E75">
-        <v>-23.24028096070231</v>
+        <v>-26.17725342153409</v>
       </c>
       <c r="F75">
-        <v>0.2160082501761025</v>
+        <v>-1.775129363891638</v>
       </c>
       <c r="G75">
-        <v>-14.03329075182289</v>
+        <v>-14.76127468972581</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.06299391814282</v>
       </c>
       <c r="E76">
-        <v>-21.05988654728057</v>
+        <v>-26.3119628308549</v>
       </c>
       <c r="F76">
-        <v>-0.7460278302087425</v>
+        <v>-1.905169792252716</v>
       </c>
       <c r="G76">
-        <v>-15.67390092809062</v>
+        <v>-14.24605860376485</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.96698203896318</v>
       </c>
       <c r="E77">
-        <v>-21.43810288978741</v>
+        <v>-26.3405327715584</v>
       </c>
       <c r="F77">
-        <v>-0.3459810469051661</v>
+        <v>-2.099568569239496</v>
       </c>
       <c r="G77">
-        <v>-14.57046058905052</v>
+        <v>-14.72382878005547</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.86411320465019</v>
       </c>
       <c r="E78">
-        <v>-23.36641814184868</v>
+        <v>-27.11571720570367</v>
       </c>
       <c r="F78">
-        <v>0.2759257211553964</v>
+        <v>-2.143964920192535</v>
       </c>
       <c r="G78">
-        <v>-15.74669370878004</v>
+        <v>-14.34666886807259</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.76397032367525</v>
       </c>
       <c r="E79">
-        <v>-23.18451579224384</v>
+        <v>-26.83192827587813</v>
       </c>
       <c r="F79">
-        <v>-0.4347331588085079</v>
+        <v>-2.223139448184709</v>
       </c>
       <c r="G79">
-        <v>-13.58851908179165</v>
+        <v>-13.76494667439761</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.65594274746608</v>
       </c>
       <c r="E80">
-        <v>-23.89251372678736</v>
+        <v>-27.88350477047942</v>
       </c>
       <c r="F80">
-        <v>-0.4820122283232897</v>
+        <v>-2.28313892753688</v>
       </c>
       <c r="G80">
-        <v>-14.56367134774133</v>
+        <v>-13.72572676377761</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.55398039926853</v>
       </c>
       <c r="E81">
-        <v>-25.5270723418435</v>
+        <v>-28.11097407813462</v>
       </c>
       <c r="F81">
-        <v>0.1178160633504575</v>
+        <v>-2.27936322891492</v>
       </c>
       <c r="G81">
-        <v>-12.91462324495513</v>
+        <v>-13.57350468964816</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.44767403507225</v>
       </c>
       <c r="E82">
-        <v>-23.88744265575975</v>
+        <v>-28.92182836774318</v>
       </c>
       <c r="F82">
-        <v>-0.1988853620878495</v>
+        <v>-2.287863106835045</v>
       </c>
       <c r="G82">
-        <v>-14.215403240776</v>
+        <v>-13.61504163609277</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.35137965121965</v>
       </c>
       <c r="E83">
-        <v>-23.77957129801997</v>
+        <v>-29.31923669978205</v>
       </c>
       <c r="F83">
-        <v>-0.7842379333976753</v>
+        <v>-2.39146701790318</v>
       </c>
       <c r="G83">
-        <v>-14.49412372257866</v>
+        <v>-13.36528083866703</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.26394326381611</v>
       </c>
       <c r="E84">
-        <v>-25.91301781062585</v>
+        <v>-29.85512140381335</v>
       </c>
       <c r="F84">
-        <v>0.1588003689713659</v>
+        <v>-2.336411235210916</v>
       </c>
       <c r="G84">
-        <v>-14.17014859403364</v>
+        <v>-13.31032074890721</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.19146423900952</v>
       </c>
       <c r="E85">
-        <v>-26.56487678769166</v>
+        <v>-30.28266336061952</v>
       </c>
       <c r="F85">
-        <v>-0.1054513176238848</v>
+        <v>-2.221090895597586</v>
       </c>
       <c r="G85">
-        <v>-14.15137211893436</v>
+        <v>-12.79919700509283</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.14426833464022</v>
       </c>
       <c r="E86">
-        <v>-28.84840166812588</v>
+        <v>-31.35634947570853</v>
       </c>
       <c r="F86">
-        <v>-0.317584612337199</v>
+        <v>-2.288536569533521</v>
       </c>
       <c r="G86">
-        <v>-13.16827666256622</v>
+        <v>-12.88556826840063</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.11624498721235</v>
       </c>
       <c r="E87">
-        <v>-27.19961622767653</v>
+        <v>-32.0260008100899</v>
       </c>
       <c r="F87">
-        <v>-1.082250561861423</v>
+        <v>-2.207416206512172</v>
       </c>
       <c r="G87">
-        <v>-12.80149184958841</v>
+        <v>-12.79094313606802</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.12349889079556</v>
       </c>
       <c r="E88">
-        <v>-31.99635518765328</v>
+        <v>-32.67821488672399</v>
       </c>
       <c r="F88">
-        <v>-0.4458929244590228</v>
+        <v>-2.248856942572022</v>
       </c>
       <c r="G88">
-        <v>-12.44053682928257</v>
+        <v>-12.74599655718741</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.15575086700867</v>
       </c>
       <c r="E89">
-        <v>-30.66211113028416</v>
+        <v>-33.59284962091737</v>
       </c>
       <c r="F89">
-        <v>0.1795675397595495</v>
+        <v>-2.448085101517123</v>
       </c>
       <c r="G89">
-        <v>-12.57177634913324</v>
+        <v>-12.42109853042943</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.22826270247427</v>
       </c>
       <c r="E90">
-        <v>-31.96499844215083</v>
+        <v>-34.6648993707444</v>
       </c>
       <c r="F90">
-        <v>-0.1699910787107999</v>
+        <v>-2.55507786363011</v>
       </c>
       <c r="G90">
-        <v>-11.70994345216084</v>
+        <v>-12.74596522825232</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.33386902650128</v>
       </c>
       <c r="E91">
-        <v>-33.31168967386046</v>
+        <v>-35.62961975690955</v>
       </c>
       <c r="F91">
-        <v>-0.4283646702157853</v>
+        <v>-2.717426277435174</v>
       </c>
       <c r="G91">
-        <v>-12.28566746013773</v>
+        <v>-12.67571792353923</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.48014849271292</v>
       </c>
       <c r="E92">
-        <v>-34.2718352977513</v>
+        <v>-36.97202072132063</v>
       </c>
       <c r="F92">
-        <v>-0.8790727471397739</v>
+        <v>-2.659578896595476</v>
       </c>
       <c r="G92">
-        <v>-12.92936873040573</v>
+        <v>-12.32961151309535</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.66834761207105</v>
       </c>
       <c r="E93">
-        <v>-35.3574785082445</v>
+        <v>-38.08795953182279</v>
       </c>
       <c r="F93">
-        <v>-0.5800246594225272</v>
+        <v>-2.585227951989804</v>
       </c>
       <c r="G93">
-        <v>-12.15564454726651</v>
+        <v>-12.25869455239464</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.88578832123687</v>
       </c>
       <c r="E94">
-        <v>-38.00377601487418</v>
+        <v>-40.00976462513238</v>
       </c>
       <c r="F94">
-        <v>-0.1681951781815306</v>
+        <v>-2.742453741775956</v>
       </c>
       <c r="G94">
-        <v>-12.13816300148442</v>
+        <v>-12.49276346945549</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.13573135999989</v>
       </c>
       <c r="E95">
-        <v>-37.41420482465248</v>
+        <v>-41.34437416509809</v>
       </c>
       <c r="F95">
-        <v>-0.6418589725718991</v>
+        <v>-3.222928372952142</v>
       </c>
       <c r="G95">
-        <v>-12.83686352268111</v>
+        <v>-12.91011448904627</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.38723402994381</v>
       </c>
       <c r="E96">
-        <v>-42.17039390585926</v>
+        <v>-42.90267982023038</v>
       </c>
       <c r="F96">
-        <v>-1.151369537951013</v>
+        <v>-2.993536043401499</v>
       </c>
       <c r="G96">
-        <v>-11.76303424879342</v>
+        <v>-12.87321814111236</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.63429602323385</v>
       </c>
       <c r="E97">
-        <v>-43.56224715751508</v>
+        <v>-44.03970863784001</v>
       </c>
       <c r="F97">
-        <v>-1.033679239198274</v>
+        <v>-3.001422101076151</v>
       </c>
       <c r="G97">
-        <v>-12.89637544563554</v>
+        <v>-12.9045549084395</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.83220287781252</v>
       </c>
       <c r="E98">
-        <v>-45.92575769655134</v>
+        <v>-46.20907627519433</v>
       </c>
       <c r="F98">
-        <v>-1.9976329901206</v>
+        <v>-3.169402584852849</v>
       </c>
       <c r="G98">
-        <v>-12.74467160430742</v>
+        <v>-13.10456927305387</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.97039231725809</v>
       </c>
       <c r="E99">
-        <v>-45.87410836051577</v>
+        <v>-47.35661790896994</v>
       </c>
       <c r="F99">
-        <v>-0.9839589709474417</v>
+        <v>-3.390141788513847</v>
       </c>
       <c r="G99">
-        <v>-12.36859645670215</v>
+        <v>-13.00633217557946</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.0030590400173</v>
       </c>
       <c r="E100">
-        <v>-48.7735825145985</v>
+        <v>-49.25837752782025</v>
       </c>
       <c r="F100">
-        <v>-0.8627953276747636</v>
+        <v>-3.493481450380488</v>
       </c>
       <c r="G100">
-        <v>-12.66352444092644</v>
+        <v>-13.23722381647293</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.92928126409082</v>
       </c>
       <c r="E101">
-        <v>-49.33848259124788</v>
+        <v>-50.41281453069791</v>
       </c>
       <c r="F101">
-        <v>-1.9537220624656</v>
+        <v>-3.478760533265338</v>
       </c>
       <c r="G101">
-        <v>-13.61085139102403</v>
+        <v>-13.11256206761956</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.70245665324611</v>
       </c>
       <c r="E102">
-        <v>-51.26534110443697</v>
+        <v>-52.22528841248706</v>
       </c>
       <c r="F102">
-        <v>-2.033295863545924</v>
+        <v>-3.780626726886909</v>
       </c>
       <c r="G102">
-        <v>-14.61997988708246</v>
+        <v>-13.8308157604314</v>
       </c>
     </row>
   </sheetData>
